--- a/summary/yes/exposures_meta_analysis_renal_cell_carcinoma_combined.xlsx
+++ b/summary/yes/exposures_meta_analysis_renal_cell_carcinoma_combined.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Analysis mode" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -450,7 +450,7 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData>
+  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
@@ -509,10 +509,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>green_tea</t>
-        </is>
+      <c r="A2" t="str">
+        <v>green_tea</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -526,10 +524,10 @@
       <c r="E2" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="5"/>
       <c r="J2" s="2" t="n">
         <v>549</v>
       </c>
@@ -538,10 +536,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>linoleic_acid</t>
-        </is>
+      <c r="A3" t="str">
+        <v>linoleic_acid</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -555,10 +551,10 @@
       <c r="E3" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="5"/>
       <c r="J3" s="2" t="n">
         <v>2301</v>
       </c>
@@ -567,10 +563,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>omega_6_fatty_acids</t>
-        </is>
+      <c r="A4" t="str">
+        <v>omega_6_fatty_acids</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -584,10 +578,10 @@
       <c r="E4" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="5"/>
       <c r="J4" s="2" t="n">
         <v>2301</v>
       </c>
@@ -596,10 +590,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>tomato</t>
-        </is>
+      <c r="A5" t="str">
+        <v>tomato</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -611,12 +603,12 @@
         <v>0.31</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
+        <v>0.81</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="5"/>
       <c r="J5" s="2" t="n">
         <v>672</v>
       </c>
@@ -625,10 +617,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>selenium</t>
-        </is>
+      <c r="A6" t="str">
+        <v>selenium</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
@@ -642,12 +632,12 @@
       <c r="E6" s="3" t="n">
         <v>7.148481810757238</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
       <c r="H6" s="4" t="n">
         <v>98.91</v>
       </c>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="I6" s="5"/>
       <c r="J6" s="2" t="n">
         <v>3471</v>
       </c>
@@ -656,10 +646,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>quercetin</t>
-        </is>
+      <c r="A7" t="str">
+        <v>quercetin</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
@@ -673,10 +661,10 @@
       <c r="E7" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="5"/>
       <c r="J7" s="2" t="n">
         <v>27111</v>
       </c>
@@ -685,10 +673,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>calcium</t>
-        </is>
+      <c r="A8" t="str">
+        <v>calcium</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>2</v>
@@ -702,12 +688,12 @@
       <c r="E8" s="3" t="n">
         <v>2.40223607137391</v>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
       <c r="H8" s="4" t="n">
         <v>93.7</v>
       </c>
-      <c r="I8" s="5" t="inlineStr"/>
+      <c r="I8" s="5"/>
       <c r="J8" s="2" t="n">
         <v>2273</v>
       </c>
@@ -716,10 +702,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>vitamin_b12</t>
-        </is>
+      <c r="A9" t="str">
+        <v>vitamin_b12</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>2</v>
@@ -733,12 +717,12 @@
       <c r="E9" s="3" t="n">
         <v>0.8535083103545701</v>
       </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
       <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="5" t="inlineStr"/>
+      <c r="I9" s="5"/>
       <c r="J9" s="2" t="n">
         <v>1959</v>
       </c>
@@ -747,10 +731,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>eggs</t>
-        </is>
+      <c r="A10" t="str">
+        <v>eggs</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
@@ -764,10 +746,10 @@
       <c r="E10" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="5"/>
       <c r="J10" s="2" t="n">
         <v>1812</v>
       </c>
@@ -776,10 +758,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>vitamin_e</t>
-        </is>
+      <c r="A11" t="str">
+        <v>vitamin_e</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>4</v>
@@ -813,10 +793,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>anti_inflammatory_diet</t>
-        </is>
+      <c r="A12" t="str">
+        <v>anti_inflammatory_diet</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
@@ -830,10 +808,10 @@
       <c r="E12" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="5"/>
       <c r="J12" s="2" t="n">
         <v>71421</v>
       </c>
@@ -842,10 +820,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>vitamin_b1</t>
-        </is>
+      <c r="A13" t="str">
+        <v>vitamin_b1</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>2</v>
@@ -859,12 +835,12 @@
       <c r="E13" s="3" t="n">
         <v>0.9196151607361948</v>
       </c>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
       <c r="H13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="5" t="inlineStr"/>
+      <c r="I13" s="5"/>
       <c r="J13" s="2" t="n">
         <v>4597</v>
       </c>
@@ -873,10 +849,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
+      <c r="A14" t="str">
+        <v>tea</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>4</v>
@@ -910,10 +884,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>alcohol</t>
-        </is>
+      <c r="A15" t="str">
+        <v>alcohol</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>20</v>
@@ -947,10 +919,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>vitamin_b6</t>
-        </is>
+      <c r="A16" t="str">
+        <v>vitamin_b6</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>4</v>
@@ -984,10 +954,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>vitamin_c</t>
-        </is>
+      <c r="A17" t="str">
+        <v>vitamin_c</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>5</v>
@@ -1021,10 +989,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>pyridoxal_5_phosphate_plp</t>
-        </is>
+      <c r="A18" t="str">
+        <v>pyridoxal_5_phosphate_plp</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -1038,10 +1004,10 @@
       <c r="E18" s="3" t="n">
         <v>0.87</v>
       </c>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="5"/>
       <c r="J18" s="2" t="n">
         <v>910</v>
       </c>
@@ -1050,10 +1016,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>folic_acid</t>
-        </is>
+      <c r="A19" t="str">
+        <v>folic_acid</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>6</v>
@@ -1087,10 +1051,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>lutein</t>
-        </is>
+      <c r="A20" t="str">
+        <v>lutein</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>5</v>
@@ -1124,10 +1086,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>betaine</t>
-        </is>
+      <c r="A21" t="str">
+        <v>betaine</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -1141,10 +1101,10 @@
       <c r="E21" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="5"/>
       <c r="J21" s="2" t="n">
         <v>77208</v>
       </c>
@@ -1153,10 +1113,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>choline</t>
-        </is>
+      <c r="A22" t="str">
+        <v>choline</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -1170,10 +1128,10 @@
       <c r="E22" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="5"/>
       <c r="J22" s="2" t="n">
         <v>77208</v>
       </c>
@@ -1182,10 +1140,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>zeaxanthin</t>
-        </is>
+      <c r="A23" t="str">
+        <v>zeaxanthin</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>2</v>
@@ -1199,12 +1155,12 @@
       <c r="E23" s="3" t="n">
         <v>0.9303448082414207</v>
       </c>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
       <c r="H23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="5" t="inlineStr"/>
+      <c r="I23" s="5"/>
       <c r="J23" s="2" t="n">
         <v>781129</v>
       </c>
@@ -1213,10 +1169,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>vitamin_b3</t>
-        </is>
+      <c r="A24" t="str">
+        <v>vitamin_b3</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -1230,10 +1184,10 @@
       <c r="E24" s="3" t="n">
         <v>1.07</v>
       </c>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="5"/>
       <c r="J24" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1242,10 +1196,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>vitamin_d</t>
-        </is>
+      <c r="A25" t="str">
+        <v>vitamin_d</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>9</v>
@@ -1279,10 +1231,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>vitamin_b2</t>
-        </is>
+      <c r="A26" t="str">
+        <v>vitamin_b2</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>3</v>
@@ -1316,10 +1266,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>total_dietary_fiber_intake</t>
-        </is>
+      <c r="A27" t="str">
+        <v>total_dietary_fiber_intake</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>2</v>
@@ -1333,12 +1281,12 @@
       <c r="E27" s="3" t="n">
         <v>1.116389703847493</v>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
       <c r="H27" s="4" t="n">
         <v>59.38</v>
       </c>
-      <c r="I27" s="5" t="inlineStr"/>
+      <c r="I27" s="5"/>
       <c r="J27" s="2" t="n">
         <v>4410</v>
       </c>
@@ -1347,10 +1295,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>insoluble_dietary_fiber_intake</t>
-        </is>
+      <c r="A28" t="str">
+        <v>insoluble_dietary_fiber_intake</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
@@ -1364,10 +1310,10 @@
       <c r="E28" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="4" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="5"/>
       <c r="J28" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1376,10 +1322,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>polyunsaturated_fat_pufa</t>
-        </is>
+      <c r="A29" t="str">
+        <v>polyunsaturated_fat_pufa</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>3</v>
@@ -1413,10 +1357,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>beta_carotene</t>
-        </is>
+      <c r="A30" t="str">
+        <v>beta_carotene</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>5</v>
@@ -1440,7 +1382,7 @@
         <v>87.95</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>0.7478484537865679</v>
+        <v>0.747848453786568</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>881922</v>
@@ -1450,10 +1392,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>sugar_sweetened_beverage_intake</t>
-        </is>
+      <c r="A31" t="str">
+        <v>sugar_sweetened_beverage_intake</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
@@ -1462,15 +1402,15 @@
         <v>0.99</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="4" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="5"/>
       <c r="J31" s="2" t="n">
         <v>389220</v>
       </c>
@@ -1479,10 +1419,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>lycopene</t>
-        </is>
+      <c r="A32" t="str">
+        <v>lycopene</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>3</v>
@@ -1503,7 +1441,7 @@
         <v>46.47162678478706</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>74.26000000000001</v>
+        <v>74.26</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>0.5668230804465441</v>
@@ -1516,10 +1454,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>animal_protein_intake</t>
-        </is>
+      <c r="A33" t="str">
+        <v>animal_protein_intake</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
@@ -1533,10 +1469,10 @@
       <c r="E33" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="5"/>
       <c r="J33" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1545,10 +1481,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>processed_meat_intake</t>
-        </is>
+      <c r="A34" t="str">
+        <v>processed_meat_intake</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>6</v>
@@ -1569,7 +1503,7 @@
         <v>2.099663439889117</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>77.01000000000001</v>
+        <v>77.01</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>0.009615835655054888</v>
@@ -1582,10 +1516,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>vitamin_a</t>
-        </is>
+      <c r="A35" t="str">
+        <v>vitamin_a</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>2</v>
@@ -1599,12 +1531,12 @@
       <c r="E35" s="3" t="n">
         <v>2.865377201601115</v>
       </c>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
       <c r="H35" s="4" t="n">
         <v>92.64</v>
       </c>
-      <c r="I35" s="5" t="inlineStr"/>
+      <c r="I35" s="5"/>
       <c r="J35" s="2" t="n">
         <v>4597</v>
       </c>
@@ -1613,10 +1545,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>potassium</t>
-        </is>
+      <c r="A36" t="str">
+        <v>potassium</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
@@ -1630,10 +1560,10 @@
       <c r="E36" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="4" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="5"/>
       <c r="J36" s="2" t="n">
         <v>120852</v>
       </c>
@@ -1642,10 +1572,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dietary_protein_intake</t>
-        </is>
+      <c r="A37" t="str">
+        <v>dietary_protein_intake</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>2</v>
@@ -1659,12 +1587,12 @@
       <c r="E37" s="3" t="n">
         <v>2.253760151959979</v>
       </c>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
       <c r="H37" s="4" t="n">
         <v>66.34</v>
       </c>
-      <c r="I37" s="5" t="inlineStr"/>
+      <c r="I37" s="5"/>
       <c r="J37" s="2" t="n">
         <v>776349</v>
       </c>
@@ -1673,10 +1601,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>yogurt</t>
-        </is>
+      <c r="A38" t="str">
+        <v>yogurt</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -1690,10 +1616,10 @@
       <c r="E38" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="5"/>
       <c r="J38" s="2" t="n">
         <v>1812</v>
       </c>
@@ -1702,107 +1628,101 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>monounsaturated_fat_mufa</t>
-        </is>
+      <c r="A39" t="str">
+        <v>ultra_processed_food_intake</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C39" s="3" t="n">
+        <v>1.3752011344215098</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>1.02009932499359</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>1.8541011066724407</v>
+      </c>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="5"/>
+      <c r="J39" s="2" t="n">
+        <v>647537</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>monounsaturated_fat_mufa</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>1.39096812846378</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>0.8185670233008897</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>2.363633373110901</v>
       </c>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="4" t="n">
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="4" t="n">
         <v>80.2</v>
       </c>
-      <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="2" t="n">
+      <c r="I40" s="5"/>
+      <c r="J40" s="2" t="n">
         <v>777095</v>
       </c>
-      <c r="K39" s="2" t="n">
+      <c r="K40" s="2" t="n">
         <v>1801</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>red_meat</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
+    <row r="41">
+      <c r="A41" t="str">
+        <v>red_meat</v>
+      </c>
+      <c r="B41" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="C41" s="3" t="n">
         <v>1.428035894777088</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>1.125806874101985</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>1.811399951166991</v>
       </c>
-      <c r="F40" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>0.6711000405372343</v>
       </c>
-      <c r="G40" s="3" t="n">
+      <c r="G41" s="3" t="n">
         <v>3.03872208849711</v>
       </c>
-      <c r="H40" s="4" t="n">
+      <c r="H41" s="4" t="n">
         <v>81.58</v>
       </c>
-      <c r="I40" s="5" t="n">
+      <c r="I41" s="5" t="n">
         <v>0.01776300266501832</v>
       </c>
-      <c r="J40" s="2" t="n">
+      <c r="J41" s="2" t="n">
         <v>1768446</v>
       </c>
-      <c r="K40" s="2" t="n">
+      <c r="K41" s="2" t="n">
         <v>5800</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>docosahexaenoic_acid</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="2" t="n">
-        <v>84063</v>
-      </c>
-      <c r="K41" s="2" t="n">
-        <v>262</v>
-      </c>
-    </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>omega_3_fatty_acids</t>
-        </is>
+      <c r="A42" t="str">
+        <v>docosahexaenoic_acid</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>1</v>
@@ -1814,12 +1734,12 @@
         <v>1.07</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr"/>
+        <v>2.27</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="5"/>
       <c r="J42" s="2" t="n">
         <v>84063</v>
       </c>
@@ -1828,39 +1748,35 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>oleic_acid</t>
-        </is>
+      <c r="A43" t="str">
+        <v>omega_3_fatty_acids</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1.9</v>
+        <v>1.56</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr"/>
+        <v>2.28</v>
+      </c>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="5"/>
       <c r="J43" s="2" t="n">
-        <v>2143</v>
+        <v>84063</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>323</v>
+        <v>262</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>omega_9_fatty_acids</t>
-        </is>
+      <c r="A44" t="str">
+        <v>oleic_acid</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>1</v>
@@ -1874,10 +1790,10 @@
       <c r="E44" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="4" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="5"/>
       <c r="J44" s="2" t="n">
         <v>2143</v>
       </c>
@@ -1886,73 +1802,96 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>carnitine</t>
-        </is>
+      <c r="A45" t="str">
+        <v>omega_9_fatty_acids</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C45" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="2" t="n">
+        <v>2143</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>carnitine</v>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>2.39</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>1.39</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>4.13</v>
       </c>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="4" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="2" t="n">
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="2" t="n">
         <v>534</v>
       </c>
-      <c r="K45" s="2" t="n">
+      <c r="K46" s="2" t="n">
         <v>267</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
+    <row r="47">
+      <c r="A47" t="str">
+        <v>dairy</v>
+      </c>
+      <c r="B47" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="C47" s="3" t="n">
         <v>2.715293362405407</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>1.217987613870554</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>6.052673044477135</v>
       </c>
-      <c r="F46" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>0.0003047814843853535</v>
       </c>
-      <c r="G46" s="3" t="n">
+      <c r="G47" s="3" t="n">
         <v>24190.50507215516</v>
       </c>
-      <c r="H46" s="4" t="n">
+      <c r="H47" s="4" t="n">
         <v>73.78</v>
       </c>
-      <c r="I46" s="5" t="n">
+      <c r="I47" s="5" t="n">
         <v>0.1029158875214485</v>
       </c>
-      <c r="J46" s="2" t="n">
+      <c r="J47" s="2" t="n">
         <v>3506</v>
       </c>
-      <c r="K46" s="2" t="n">
+      <c r="K47" s="2" t="n">
         <v>1009</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K46"/>
+  <autoFilter ref="A1:K47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/summary/yes/exposures_meta_analysis_renal_cell_carcinoma_combined.xlsx
+++ b/summary/yes/exposures_meta_analysis_renal_cell_carcinoma_combined.xlsx
@@ -450,7 +450,7 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
@@ -509,8 +509,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>green_tea</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>green_tea</t>
+        </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -524,10 +526,10 @@
       <c r="E2" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="5"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr"/>
       <c r="J2" s="2" t="n">
         <v>549</v>
       </c>
@@ -536,8 +538,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>linoleic_acid</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>linoleic_acid</t>
+        </is>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -551,10 +555,10 @@
       <c r="E3" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="5"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr"/>
       <c r="J3" s="2" t="n">
         <v>2301</v>
       </c>
@@ -563,8 +567,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>omega_6_fatty_acids</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>omega_6_fatty_acids</t>
+        </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -578,10 +584,10 @@
       <c r="E4" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="5"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="2" t="n">
         <v>2301</v>
       </c>
@@ -590,8 +596,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>tomato</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -603,12 +611,12 @@
         <v>0.31</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="5"/>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
       <c r="J5" s="2" t="n">
         <v>672</v>
       </c>
@@ -617,8 +625,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>selenium</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>selenium</t>
+        </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
@@ -632,12 +642,12 @@
       <c r="E6" s="3" t="n">
         <v>7.148481810757238</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="4" t="n">
         <v>98.91</v>
       </c>
-      <c r="I6" s="5"/>
+      <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="2" t="n">
         <v>3471</v>
       </c>
@@ -646,8 +656,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>quercetin</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>quercetin</t>
+        </is>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
@@ -661,10 +673,10 @@
       <c r="E7" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="5"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
       <c r="J7" s="2" t="n">
         <v>27111</v>
       </c>
@@ -673,8 +685,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>calcium</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>2</v>
@@ -688,12 +702,12 @@
       <c r="E8" s="3" t="n">
         <v>2.40223607137391</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="4" t="n">
         <v>93.7</v>
       </c>
-      <c r="I8" s="5"/>
+      <c r="I8" s="5" t="inlineStr"/>
       <c r="J8" s="2" t="n">
         <v>2273</v>
       </c>
@@ -702,8 +716,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>vitamin_b12</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>vitamin_b12</t>
+        </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>2</v>
@@ -717,12 +733,12 @@
       <c r="E9" s="3" t="n">
         <v>0.8535083103545701</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="5"/>
+      <c r="I9" s="5" t="inlineStr"/>
       <c r="J9" s="2" t="n">
         <v>1959</v>
       </c>
@@ -731,8 +747,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>eggs</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>eggs</t>
+        </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
@@ -746,10 +764,10 @@
       <c r="E10" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="5"/>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
       <c r="J10" s="2" t="n">
         <v>1812</v>
       </c>
@@ -758,8 +776,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>vitamin_e</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>vitamin_e</t>
+        </is>
       </c>
       <c r="B11" s="2" t="n">
         <v>4</v>
@@ -793,8 +813,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>anti_inflammatory_diet</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>anti_inflammatory_diet</t>
+        </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
@@ -808,10 +830,10 @@
       <c r="E12" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="5"/>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
       <c r="J12" s="2" t="n">
         <v>71421</v>
       </c>
@@ -820,8 +842,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>vitamin_b1</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>vitamin_b1</t>
+        </is>
       </c>
       <c r="B13" s="2" t="n">
         <v>2</v>
@@ -835,12 +859,12 @@
       <c r="E13" s="3" t="n">
         <v>0.9196151607361948</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="5"/>
+      <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="2" t="n">
         <v>4597</v>
       </c>
@@ -849,8 +873,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>tea</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tea</t>
+        </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>4</v>
@@ -874,7 +900,7 @@
         <v>77.67</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.406094525741328</v>
+        <v>0.4060945257413278</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>804643</v>
@@ -884,8 +910,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>alcohol</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>alcohol</t>
+        </is>
       </c>
       <c r="B15" s="2" t="n">
         <v>20</v>
@@ -909,7 +937,7 @@
         <v>54.62</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.0025910796269718</v>
+        <v>0.002591079626971808</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>3783725</v>
@@ -919,8 +947,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
-        <v>vitamin_b6</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>vitamin_b6</t>
+        </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>4</v>
@@ -944,7 +974,7 @@
         <v>81.53</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.9763185191218324</v>
+        <v>0.9763185191218329</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>4771</v>
@@ -954,8 +984,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
-        <v>vitamin_c</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>vitamin_c</t>
+        </is>
       </c>
       <c r="B17" s="2" t="n">
         <v>5</v>
@@ -989,8 +1021,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
-        <v>pyridoxal_5_phosphate_plp</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>pyridoxal_5_phosphate_plp</t>
+        </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -1004,10 +1038,10 @@
       <c r="E18" s="3" t="n">
         <v>0.87</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="5"/>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="2" t="n">
         <v>910</v>
       </c>
@@ -1016,8 +1050,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
-        <v>folic_acid</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>folic_acid</t>
+        </is>
       </c>
       <c r="B19" s="2" t="n">
         <v>6</v>
@@ -1041,7 +1077,7 @@
         <v>82.8</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0.502972556082802</v>
+        <v>0.5029725560828019</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>84212</v>
@@ -1051,8 +1087,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
-        <v>lutein</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>lutein</t>
+        </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>5</v>
@@ -1086,8 +1124,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
-        <v>betaine</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>betaine</t>
+        </is>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -1101,10 +1141,10 @@
       <c r="E21" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="5"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="2" t="n">
         <v>77208</v>
       </c>
@@ -1113,8 +1153,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str">
-        <v>choline</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>choline</t>
+        </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -1128,10 +1170,10 @@
       <c r="E22" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="5"/>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="2" t="n">
         <v>77208</v>
       </c>
@@ -1140,8 +1182,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
-        <v>zeaxanthin</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>zeaxanthin</t>
+        </is>
       </c>
       <c r="B23" s="2" t="n">
         <v>2</v>
@@ -1155,12 +1199,12 @@
       <c r="E23" s="3" t="n">
         <v>0.9303448082414207</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="5"/>
+      <c r="I23" s="5" t="inlineStr"/>
       <c r="J23" s="2" t="n">
         <v>781129</v>
       </c>
@@ -1169,8 +1213,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
-        <v>vitamin_b3</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>vitamin_b3</t>
+        </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -1184,10 +1230,10 @@
       <c r="E24" s="3" t="n">
         <v>1.07</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="5"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1196,8 +1242,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
-        <v>vitamin_d</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>vitamin_d</t>
+        </is>
       </c>
       <c r="B25" s="2" t="n">
         <v>9</v>
@@ -1221,7 +1269,7 @@
         <v>61.07</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>0.8617561858267221</v>
+        <v>0.8617561858267218</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>153812</v>
@@ -1231,8 +1279,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
-        <v>vitamin_b2</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>vitamin_b2</t>
+        </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>3</v>
@@ -1256,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>0.2763513833592365</v>
+        <v>0.2763513833592364</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>3861</v>
@@ -1266,8 +1316,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
-        <v>total_dietary_fiber_intake</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>total_dietary_fiber_intake</t>
+        </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>2</v>
@@ -1281,12 +1333,12 @@
       <c r="E27" s="3" t="n">
         <v>1.116389703847493</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
       <c r="H27" s="4" t="n">
         <v>59.38</v>
       </c>
-      <c r="I27" s="5"/>
+      <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="2" t="n">
         <v>4410</v>
       </c>
@@ -1295,8 +1347,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
-        <v>insoluble_dietary_fiber_intake</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>insoluble_dietary_fiber_intake</t>
+        </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
@@ -1310,10 +1364,10 @@
       <c r="E28" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="5"/>
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
       <c r="J28" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1322,8 +1376,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str">
-        <v>polyunsaturated_fat_pufa</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>polyunsaturated_fat_pufa</t>
+        </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>3</v>
@@ -1357,8 +1413,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str">
-        <v>beta_carotene</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>beta_carotene</t>
+        </is>
       </c>
       <c r="B30" s="2" t="n">
         <v>5</v>
@@ -1382,7 +1440,7 @@
         <v>87.95</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>0.747848453786568</v>
+        <v>0.7478484537865681</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>881922</v>
@@ -1392,8 +1450,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="str">
-        <v>sugar_sweetened_beverage_intake</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sugar_sweetened_beverage_intake</t>
+        </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
@@ -1402,15 +1462,15 @@
         <v>0.99</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.94</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="5"/>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="2" t="n">
         <v>389220</v>
       </c>
@@ -1419,8 +1479,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str">
-        <v>lycopene</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>lycopene</t>
+        </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>3</v>
@@ -1441,10 +1503,10 @@
         <v>46.47162678478706</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>74.26</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>0.5668230804465441</v>
+        <v>0.5668230804465442</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>873444</v>
@@ -1454,8 +1516,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str">
-        <v>animal_protein_intake</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>animal_protein_intake</t>
+        </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
@@ -1469,10 +1533,10 @@
       <c r="E33" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="5"/>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1481,8 +1545,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
-        <v>processed_meat_intake</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>processed_meat_intake</t>
+        </is>
       </c>
       <c r="B34" s="2" t="n">
         <v>6</v>
@@ -1497,16 +1563,16 @@
         <v>1.410014516884722</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.6286522322</v>
+        <v>0.6286522321999999</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>2.099663439889117</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>77.01</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>0.009615835655054888</v>
+        <v>0.009615835655054882</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>1766660</v>
@@ -1516,8 +1582,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
-        <v>vitamin_a</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>vitamin_a</t>
+        </is>
       </c>
       <c r="B35" s="2" t="n">
         <v>2</v>
@@ -1531,12 +1599,12 @@
       <c r="E35" s="3" t="n">
         <v>2.865377201601115</v>
       </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
       <c r="H35" s="4" t="n">
         <v>92.64</v>
       </c>
-      <c r="I35" s="5"/>
+      <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="2" t="n">
         <v>4597</v>
       </c>
@@ -1545,8 +1613,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
-        <v>potassium</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>potassium</t>
+        </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
@@ -1560,10 +1630,10 @@
       <c r="E36" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="5"/>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="2" t="n">
         <v>120852</v>
       </c>
@@ -1572,8 +1642,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
-        <v>dietary_protein_intake</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dietary_protein_intake</t>
+        </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>2</v>
@@ -1587,12 +1659,12 @@
       <c r="E37" s="3" t="n">
         <v>2.253760151959979</v>
       </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
       <c r="H37" s="4" t="n">
         <v>66.34</v>
       </c>
-      <c r="I37" s="5"/>
+      <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="2" t="n">
         <v>776349</v>
       </c>
@@ -1601,8 +1673,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
-        <v>yogurt</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>yogurt</t>
+        </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -1616,10 +1690,10 @@
       <c r="E38" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="5"/>
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="2" t="n">
         <v>1812</v>
       </c>
@@ -1628,27 +1702,29 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
-        <v>ultra_processed_food_intake</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ultra_processed_food_intake</t>
+        </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1.3752011344215098</v>
+        <v>1.37520113442151</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>1.02009932499359</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1.8541011066724407</v>
-      </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
+        <v>1.854101106672441</v>
+      </c>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="5"/>
+      <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="2" t="n">
         <v>647537</v>
       </c>
@@ -1657,8 +1733,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
-        <v>monounsaturated_fat_mufa</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>monounsaturated_fat_mufa</t>
+        </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>2</v>
@@ -1672,12 +1750,12 @@
       <c r="E40" s="3" t="n">
         <v>2.363633373110901</v>
       </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr"/>
       <c r="H40" s="4" t="n">
         <v>80.2</v>
       </c>
-      <c r="I40" s="5"/>
+      <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="2" t="n">
         <v>777095</v>
       </c>
@@ -1686,8 +1764,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str">
-        <v>red_meat</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>red_meat</t>
+        </is>
       </c>
       <c r="B41" s="2" t="n">
         <v>6</v>
@@ -1721,8 +1801,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="str">
-        <v>docosahexaenoic_acid</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>docosahexaenoic_acid</t>
+        </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>1</v>
@@ -1736,10 +1818,10 @@
       <c r="E42" s="3" t="n">
         <v>2.27</v>
       </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="5"/>
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="2" t="n">
         <v>84063</v>
       </c>
@@ -1748,8 +1830,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="str">
-        <v>omega_3_fatty_acids</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>omega_3_fatty_acids</t>
+        </is>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
@@ -1763,10 +1847,10 @@
       <c r="E43" s="3" t="n">
         <v>2.28</v>
       </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="5"/>
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="2" t="n">
         <v>84063</v>
       </c>
@@ -1775,8 +1859,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="str">
-        <v>oleic_acid</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>oleic_acid</t>
+        </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>1</v>
@@ -1790,10 +1876,10 @@
       <c r="E44" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="5"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="2" t="n">
         <v>2143</v>
       </c>
@@ -1802,8 +1888,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="str">
-        <v>omega_9_fatty_acids</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>omega_9_fatty_acids</t>
+        </is>
       </c>
       <c r="B45" s="2" t="n">
         <v>1</v>
@@ -1817,10 +1905,10 @@
       <c r="E45" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="5"/>
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="2" t="n">
         <v>2143</v>
       </c>
@@ -1829,8 +1917,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="str">
-        <v>carnitine</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>carnitine</t>
+        </is>
       </c>
       <c r="B46" s="2" t="n">
         <v>1</v>
@@ -1844,10 +1934,10 @@
       <c r="E46" s="3" t="n">
         <v>4.13</v>
       </c>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="5"/>
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="2" t="n">
         <v>534</v>
       </c>
@@ -1856,8 +1946,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="str">
-        <v>dairy</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
       </c>
       <c r="B47" s="2" t="n">
         <v>3</v>

--- a/summary/yes/exposures_meta_analysis_renal_cell_carcinoma_combined.xlsx
+++ b/summary/yes/exposures_meta_analysis_renal_cell_carcinoma_combined.xlsx
@@ -450,7 +450,7 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData>
+  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
@@ -509,10 +509,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>green_tea</t>
-        </is>
+      <c r="A2" t="str">
+        <v>green_tea</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -526,10 +524,10 @@
       <c r="E2" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="5"/>
       <c r="J2" s="2" t="n">
         <v>549</v>
       </c>
@@ -538,10 +536,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>linoleic_acid</t>
-        </is>
+      <c r="A3" t="str">
+        <v>linoleic_acid</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -555,10 +551,10 @@
       <c r="E3" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="5"/>
       <c r="J3" s="2" t="n">
         <v>2301</v>
       </c>
@@ -567,10 +563,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>omega_6_fatty_acids</t>
-        </is>
+      <c r="A4" t="str">
+        <v>omega_6_fatty_acids</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -584,10 +578,10 @@
       <c r="E4" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="5"/>
       <c r="J4" s="2" t="n">
         <v>2301</v>
       </c>
@@ -596,10 +590,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>tomato</t>
-        </is>
+      <c r="A5" t="str">
+        <v>tomato</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -611,12 +603,12 @@
         <v>0.31</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
+        <v>0.81</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="5"/>
       <c r="J5" s="2" t="n">
         <v>672</v>
       </c>
@@ -625,10 +617,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>selenium</t>
-        </is>
+      <c r="A6" t="str">
+        <v>selenium</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
@@ -642,12 +632,12 @@
       <c r="E6" s="3" t="n">
         <v>7.148481810757238</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
       <c r="H6" s="4" t="n">
         <v>98.91</v>
       </c>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="I6" s="5"/>
       <c r="J6" s="2" t="n">
         <v>3471</v>
       </c>
@@ -656,10 +646,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>quercetin</t>
-        </is>
+      <c r="A7" t="str">
+        <v>quercetin</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
@@ -673,10 +661,10 @@
       <c r="E7" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="5"/>
       <c r="J7" s="2" t="n">
         <v>27111</v>
       </c>
@@ -685,10 +673,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>calcium</t>
-        </is>
+      <c r="A8" t="str">
+        <v>calcium</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>2</v>
@@ -702,12 +688,12 @@
       <c r="E8" s="3" t="n">
         <v>2.40223607137391</v>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
       <c r="H8" s="4" t="n">
         <v>93.7</v>
       </c>
-      <c r="I8" s="5" t="inlineStr"/>
+      <c r="I8" s="5"/>
       <c r="J8" s="2" t="n">
         <v>2273</v>
       </c>
@@ -716,10 +702,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>vitamin_b12</t>
-        </is>
+      <c r="A9" t="str">
+        <v>vitamin_b12</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>2</v>
@@ -733,12 +717,12 @@
       <c r="E9" s="3" t="n">
         <v>0.8535083103545701</v>
       </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
       <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="5" t="inlineStr"/>
+      <c r="I9" s="5"/>
       <c r="J9" s="2" t="n">
         <v>1959</v>
       </c>
@@ -747,10 +731,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>eggs</t>
-        </is>
+      <c r="A10" t="str">
+        <v>eggs</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
@@ -764,10 +746,10 @@
       <c r="E10" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="5"/>
       <c r="J10" s="2" t="n">
         <v>1812</v>
       </c>
@@ -776,10 +758,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>vitamin_e</t>
-        </is>
+      <c r="A11" t="str">
+        <v>vitamin_e</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>4</v>
@@ -813,10 +793,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>anti_inflammatory_diet</t>
-        </is>
+      <c r="A12" t="str">
+        <v>anti_inflammatory_diet</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
@@ -830,10 +808,10 @@
       <c r="E12" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="5"/>
       <c r="J12" s="2" t="n">
         <v>71421</v>
       </c>
@@ -842,10 +820,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>vitamin_b1</t>
-        </is>
+      <c r="A13" t="str">
+        <v>vitamin_b1</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>2</v>
@@ -859,12 +835,12 @@
       <c r="E13" s="3" t="n">
         <v>0.9196151607361948</v>
       </c>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
       <c r="H13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="5" t="inlineStr"/>
+      <c r="I13" s="5"/>
       <c r="J13" s="2" t="n">
         <v>4597</v>
       </c>
@@ -873,10 +849,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
+      <c r="A14" t="str">
+        <v>tea</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>4</v>
@@ -910,47 +884,43 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>alcohol</t>
-        </is>
+      <c r="A15" t="str">
+        <v>alcohol</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.7171286688639856</v>
+        <v>0.7166985207200148</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.6528551478261688</v>
+        <v>0.6540967517572572</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.7877299113272275</v>
+        <v>0.785291729736156</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.5273554843225526</v>
+        <v>0.5315702982473368</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.975193286113776</v>
+        <v>0.9663007344388077</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>54.62</v>
+        <v>52.61</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.002591079626971808</v>
+        <v>0.0019049944016419095</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>3783725</v>
+        <v>3860985</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>11677</v>
+        <v>11926</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>vitamin_b6</t>
-        </is>
+      <c r="A16" t="str">
+        <v>vitamin_b6</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>4</v>
@@ -984,10 +954,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>vitamin_c</t>
-        </is>
+      <c r="A17" t="str">
+        <v>vitamin_c</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>5</v>
@@ -1021,10 +989,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>pyridoxal_5_phosphate_plp</t>
-        </is>
+      <c r="A18" t="str">
+        <v>pyridoxal_5_phosphate_plp</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -1038,10 +1004,10 @@
       <c r="E18" s="3" t="n">
         <v>0.87</v>
       </c>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="5"/>
       <c r="J18" s="2" t="n">
         <v>910</v>
       </c>
@@ -1050,10 +1016,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>folic_acid</t>
-        </is>
+      <c r="A19" t="str">
+        <v>folic_acid</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>6</v>
@@ -1087,10 +1051,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>lutein</t>
-        </is>
+      <c r="A20" t="str">
+        <v>lutein</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>5</v>
@@ -1124,10 +1086,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>betaine</t>
-        </is>
+      <c r="A21" t="str">
+        <v>betaine</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -1141,10 +1101,10 @@
       <c r="E21" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="5"/>
       <c r="J21" s="2" t="n">
         <v>77208</v>
       </c>
@@ -1153,10 +1113,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>choline</t>
-        </is>
+      <c r="A22" t="str">
+        <v>choline</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -1170,10 +1128,10 @@
       <c r="E22" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="5"/>
       <c r="J22" s="2" t="n">
         <v>77208</v>
       </c>
@@ -1182,10 +1140,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>zeaxanthin</t>
-        </is>
+      <c r="A23" t="str">
+        <v>zeaxanthin</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>2</v>
@@ -1199,12 +1155,12 @@
       <c r="E23" s="3" t="n">
         <v>0.9303448082414207</v>
       </c>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
       <c r="H23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="5" t="inlineStr"/>
+      <c r="I23" s="5"/>
       <c r="J23" s="2" t="n">
         <v>781129</v>
       </c>
@@ -1213,10 +1169,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>vitamin_b3</t>
-        </is>
+      <c r="A24" t="str">
+        <v>vitamin_b3</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -1230,10 +1184,10 @@
       <c r="E24" s="3" t="n">
         <v>1.07</v>
       </c>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="5"/>
       <c r="J24" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1242,10 +1196,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>vitamin_d</t>
-        </is>
+      <c r="A25" t="str">
+        <v>vitamin_d</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>9</v>
@@ -1279,10 +1231,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>vitamin_b2</t>
-        </is>
+      <c r="A26" t="str">
+        <v>vitamin_b2</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>3</v>
@@ -1316,10 +1266,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>total_dietary_fiber_intake</t>
-        </is>
+      <c r="A27" t="str">
+        <v>total_dietary_fiber_intake</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>2</v>
@@ -1333,12 +1281,12 @@
       <c r="E27" s="3" t="n">
         <v>1.116389703847493</v>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
       <c r="H27" s="4" t="n">
         <v>59.38</v>
       </c>
-      <c r="I27" s="5" t="inlineStr"/>
+      <c r="I27" s="5"/>
       <c r="J27" s="2" t="n">
         <v>4410</v>
       </c>
@@ -1347,10 +1295,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>insoluble_dietary_fiber_intake</t>
-        </is>
+      <c r="A28" t="str">
+        <v>insoluble_dietary_fiber_intake</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
@@ -1364,10 +1310,10 @@
       <c r="E28" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="4" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="5"/>
       <c r="J28" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1376,10 +1322,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>polyunsaturated_fat_pufa</t>
-        </is>
+      <c r="A29" t="str">
+        <v>polyunsaturated_fat_pufa</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>3</v>
@@ -1413,10 +1357,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>beta_carotene</t>
-        </is>
+      <c r="A30" t="str">
+        <v>beta_carotene</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>5</v>
@@ -1450,10 +1392,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>sugar_sweetened_beverage_intake</t>
-        </is>
+      <c r="A31" t="str">
+        <v>sugar_sweetened_beverage_intake</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
@@ -1462,15 +1402,15 @@
         <v>0.99</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="4" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="5"/>
       <c r="J31" s="2" t="n">
         <v>389220</v>
       </c>
@@ -1479,10 +1419,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>lycopene</t>
-        </is>
+      <c r="A32" t="str">
+        <v>lycopene</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>3</v>
@@ -1503,7 +1441,7 @@
         <v>46.47162678478706</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>74.26000000000001</v>
+        <v>74.26</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>0.5668230804465442</v>
@@ -1516,10 +1454,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>animal_protein_intake</t>
-        </is>
+      <c r="A33" t="str">
+        <v>animal_protein_intake</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
@@ -1533,10 +1469,10 @@
       <c r="E33" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="5"/>
       <c r="J33" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1545,10 +1481,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>processed_meat_intake</t>
-        </is>
+      <c r="A34" t="str">
+        <v>processed_meat_intake</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>6</v>
@@ -1569,7 +1503,7 @@
         <v>2.099663439889117</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>77.01000000000001</v>
+        <v>77.01</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>0.009615835655054882</v>
@@ -1582,10 +1516,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>vitamin_a</t>
-        </is>
+      <c r="A35" t="str">
+        <v>vitamin_a</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>2</v>
@@ -1599,12 +1531,12 @@
       <c r="E35" s="3" t="n">
         <v>2.865377201601115</v>
       </c>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
       <c r="H35" s="4" t="n">
         <v>92.64</v>
       </c>
-      <c r="I35" s="5" t="inlineStr"/>
+      <c r="I35" s="5"/>
       <c r="J35" s="2" t="n">
         <v>4597</v>
       </c>
@@ -1613,10 +1545,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>potassium</t>
-        </is>
+      <c r="A36" t="str">
+        <v>potassium</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
@@ -1630,10 +1560,10 @@
       <c r="E36" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="4" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="5"/>
       <c r="J36" s="2" t="n">
         <v>120852</v>
       </c>
@@ -1642,10 +1572,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>dietary_protein_intake</t>
-        </is>
+      <c r="A37" t="str">
+        <v>dietary_protein_intake</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>2</v>
@@ -1659,12 +1587,12 @@
       <c r="E37" s="3" t="n">
         <v>2.253760151959979</v>
       </c>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
       <c r="H37" s="4" t="n">
         <v>66.34</v>
       </c>
-      <c r="I37" s="5" t="inlineStr"/>
+      <c r="I37" s="5"/>
       <c r="J37" s="2" t="n">
         <v>776349</v>
       </c>
@@ -1673,10 +1601,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>yogurt</t>
-        </is>
+      <c r="A38" t="str">
+        <v>yogurt</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -1690,10 +1616,10 @@
       <c r="E38" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="5"/>
       <c r="J38" s="2" t="n">
         <v>1812</v>
       </c>
@@ -1702,10 +1628,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ultra_processed_food_intake</t>
-        </is>
+      <c r="A39" t="str">
+        <v>ultra_processed_food_intake</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>2</v>
@@ -1719,12 +1643,12 @@
       <c r="E39" s="3" t="n">
         <v>1.854101106672441</v>
       </c>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
       <c r="H39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="5" t="inlineStr"/>
+      <c r="I39" s="5"/>
       <c r="J39" s="2" t="n">
         <v>647537</v>
       </c>
@@ -1733,10 +1657,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>monounsaturated_fat_mufa</t>
-        </is>
+      <c r="A40" t="str">
+        <v>monounsaturated_fat_mufa</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>2</v>
@@ -1750,12 +1672,12 @@
       <c r="E40" s="3" t="n">
         <v>2.363633373110901</v>
       </c>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
       <c r="H40" s="4" t="n">
         <v>80.2</v>
       </c>
-      <c r="I40" s="5" t="inlineStr"/>
+      <c r="I40" s="5"/>
       <c r="J40" s="2" t="n">
         <v>777095</v>
       </c>
@@ -1764,10 +1686,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>red_meat</t>
-        </is>
+      <c r="A41" t="str">
+        <v>red_meat</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>6</v>
@@ -1801,10 +1721,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>docosahexaenoic_acid</t>
-        </is>
+      <c r="A42" t="str">
+        <v>docosahexaenoic_acid</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>1</v>
@@ -1818,10 +1736,10 @@
       <c r="E42" s="3" t="n">
         <v>2.27</v>
       </c>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="5"/>
       <c r="J42" s="2" t="n">
         <v>84063</v>
       </c>
@@ -1830,10 +1748,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>omega_3_fatty_acids</t>
-        </is>
+      <c r="A43" t="str">
+        <v>omega_3_fatty_acids</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
@@ -1847,10 +1763,10 @@
       <c r="E43" s="3" t="n">
         <v>2.28</v>
       </c>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="5"/>
       <c r="J43" s="2" t="n">
         <v>84063</v>
       </c>
@@ -1859,10 +1775,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>oleic_acid</t>
-        </is>
+      <c r="A44" t="str">
+        <v>oleic_acid</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>1</v>
@@ -1876,10 +1790,10 @@
       <c r="E44" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="4" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="5"/>
       <c r="J44" s="2" t="n">
         <v>2143</v>
       </c>
@@ -1888,10 +1802,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>omega_9_fatty_acids</t>
-        </is>
+      <c r="A45" t="str">
+        <v>omega_9_fatty_acids</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>1</v>
@@ -1905,10 +1817,10 @@
       <c r="E45" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="4" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="5"/>
       <c r="J45" s="2" t="n">
         <v>2143</v>
       </c>
@@ -1917,10 +1829,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>carnitine</t>
-        </is>
+      <c r="A46" t="str">
+        <v>carnitine</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>1</v>
@@ -1934,10 +1844,10 @@
       <c r="E46" s="3" t="n">
         <v>4.13</v>
       </c>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="4" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="5"/>
       <c r="J46" s="2" t="n">
         <v>534</v>
       </c>
@@ -1946,10 +1856,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
+      <c r="A47" t="str">
+        <v>dairy</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>3</v>

--- a/summary/yes/exposures_meta_analysis_renal_cell_carcinoma_combined.xlsx
+++ b/summary/yes/exposures_meta_analysis_renal_cell_carcinoma_combined.xlsx
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -49,7 +52,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -57,13 +60,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -450,1443 +462,1535 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>number estimates</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>green_tea</v>
-      </c>
-      <c r="B2" s="2" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>green_tea</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="4" t="n">
         <v>0.34</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>0.21</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>0.55</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="2" t="n">
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="5" t="inlineStr"/>
+      <c r="I2" s="6" t="inlineStr"/>
+      <c r="J2" s="3" t="n">
         <v>549</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="3" t="n">
         <v>250</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>linoleic_acid</v>
-      </c>
-      <c r="B3" s="2" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>linoleic_acid</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="2" t="n">
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="5" t="inlineStr"/>
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="3" t="n">
         <v>2301</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="3" t="n">
         <v>767</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>omega_6_fatty_acids</v>
-      </c>
-      <c r="B4" s="2" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>omega_6_fatty_acids</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="2" t="n">
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="3" t="n">
         <v>2301</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="3" t="n">
         <v>767</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>tomato</v>
-      </c>
-      <c r="B5" s="2" t="n">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>0.31</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="2" t="n">
+      <c r="E5" s="4" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="3" t="n">
         <v>672</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="3" t="n">
         <v>335</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>selenium</v>
-      </c>
-      <c r="B6" s="2" t="n">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>selenium</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="4" t="n">
         <v>0.5277144267608633</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>0.03896077142373314</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>7.148481810757238</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="4" t="n">
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="5" t="n">
         <v>98.91</v>
       </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="2" t="n">
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="3" t="n">
         <v>3471</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="3" t="n">
         <v>1543</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>quercetin</v>
-      </c>
-      <c r="B7" s="2" t="n">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>quercetin</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="2" t="n">
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="3" t="n">
         <v>27111</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="3" t="n">
         <v>228</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>calcium</v>
-      </c>
-      <c r="B8" s="2" t="n">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="4" t="n">
         <v>0.6182267372856237</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>0.159119466063619</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="4" t="n">
         <v>2.40223607137391</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="4" t="n">
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="5" t="n">
         <v>93.7</v>
       </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="2" t="n">
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="3" t="n">
         <v>2273</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="K8" s="3" t="n">
         <v>154</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>vitamin_b12</v>
-      </c>
-      <c r="B9" s="2" t="n">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>vitamin_b12</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="4" t="n">
         <v>0.6305265594747873</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="4" t="n">
         <v>0.4657994976498283</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="4" t="n">
         <v>0.8535083103545701</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="4" t="n">
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="2" t="n">
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="3" t="n">
         <v>1959</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="K9" s="3" t="n">
         <v>730</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>eggs</v>
-      </c>
-      <c r="B10" s="2" t="n">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>eggs</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="4" t="n">
         <v>0.64</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="4" t="n">
         <v>0.48</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="2" t="n">
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="3" t="n">
         <v>1812</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="K10" s="3" t="n">
         <v>777</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>vitamin_e</v>
-      </c>
-      <c r="B11" s="2" t="n">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>vitamin_e</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="4" t="n">
         <v>0.6704541234521412</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="4" t="n">
         <v>0.4526663314814308</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="4" t="n">
         <v>0.9929251454538985</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>0.1198875658458504</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>3.749419120177572</v>
-      </c>
-      <c r="H11" s="4" t="n">
+      <c r="F11" s="4" t="n">
+        <v>0.1198875658484078</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>3.749419120097587</v>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>75.61</v>
       </c>
-      <c r="I11" s="5" t="n">
-        <v>0.5015932102841117</v>
-      </c>
-      <c r="J11" s="2" t="n">
+      <c r="I11" s="6" t="n">
+        <v>0.5015932102841116</v>
+      </c>
+      <c r="J11" s="3" t="n">
         <v>127855</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="K11" s="3" t="n">
         <v>2404</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>anti_inflammatory_diet</v>
-      </c>
-      <c r="B12" s="2" t="n">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>anti_inflammatory_diet</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <v>0.52</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="2" t="n">
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="3" t="n">
         <v>71421</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="K12" s="3" t="n">
         <v>431</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>vitamin_b1</v>
-      </c>
-      <c r="B13" s="2" t="n">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>vitamin_b1</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="4" t="n">
         <v>0.7116279829325146</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="4" t="n">
         <v>0.5506807713861427</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="4" t="n">
         <v>0.9196151607361948</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="4" t="n">
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="5"/>
-      <c r="J13" s="2" t="n">
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="3" t="n">
         <v>4597</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="K13" s="3" t="n">
         <v>1909</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>tea</v>
-      </c>
-      <c r="B14" s="2" t="n">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tea</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="4" t="n">
         <v>0.7142658835761514</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="4" t="n">
         <v>0.5123229966574786</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="4" t="n">
         <v>0.9958088076649545</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>0.1670242223297662</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>3.054501588599221</v>
-      </c>
-      <c r="H14" s="4" t="n">
+      <c r="F14" s="4" t="n">
+        <v>0.1670242223327739</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>3.054501588544217</v>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>77.67</v>
       </c>
-      <c r="I14" s="5" t="n">
-        <v>0.4060945257413278</v>
-      </c>
-      <c r="J14" s="2" t="n">
+      <c r="I14" s="6" t="n">
+        <v>0.4060945257413281</v>
+      </c>
+      <c r="J14" s="3" t="n">
         <v>804643</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="K14" s="3" t="n">
         <v>2861</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>alcohol</v>
-      </c>
-      <c r="B15" s="2" t="n">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>alcohol</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="4" t="n">
         <v>0.7166985207200148</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="4" t="n">
         <v>0.6540967517572572</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="4" t="n">
         <v>0.785291729736156</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>0.5315702982473368</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>0.9663007344388077</v>
-      </c>
-      <c r="H15" s="4" t="n">
+      <c r="F15" s="4" t="n">
+        <v>0.5315702982473401</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0.9663007344388015</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>52.61</v>
       </c>
-      <c r="I15" s="5" t="n">
-        <v>0.0019049944016419095</v>
-      </c>
-      <c r="J15" s="2" t="n">
+      <c r="I15" s="6" t="n">
+        <v>0.00190499440164191</v>
+      </c>
+      <c r="J15" s="3" t="n">
         <v>3860985</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="K15" s="3" t="n">
         <v>11926</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
-        <v>vitamin_b6</v>
-      </c>
-      <c r="B16" s="2" t="n">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>vitamin_b6</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" s="4" t="n">
         <v>0.7345479521991701</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="4" t="n">
         <v>0.5184042166537559</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="4" t="n">
         <v>1.040706698318849</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>0.1585301081283082</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>3.403521895306439</v>
-      </c>
-      <c r="H16" s="4" t="n">
+      <c r="F16" s="4" t="n">
+        <v>0.1585301081313205</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>3.403521895241767</v>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>81.53</v>
       </c>
-      <c r="I16" s="5" t="n">
-        <v>0.9763185191218329</v>
-      </c>
-      <c r="J16" s="2" t="n">
+      <c r="I16" s="6" t="n">
+        <v>0.9763185191218325</v>
+      </c>
+      <c r="J16" s="3" t="n">
         <v>4771</v>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="K16" s="3" t="n">
         <v>2002</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
-        <v>vitamin_c</v>
-      </c>
-      <c r="B17" s="2" t="n">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>vitamin_c</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" s="4" t="n">
         <v>0.7585094662858782</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="4" t="n">
         <v>0.6137301147444475</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="4" t="n">
         <v>0.9374423653381478</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>0.4223806276719194</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>1.362128309758031</v>
-      </c>
-      <c r="H17" s="4" t="n">
+      <c r="F17" s="4" t="n">
+        <v>0.4223806276718763</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>1.36212830975817</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>39.11</v>
       </c>
-      <c r="I17" s="5" t="n">
-        <v>0.2965256086013334</v>
-      </c>
-      <c r="J17" s="2" t="n">
+      <c r="I17" s="6" t="n">
+        <v>0.2965256086013331</v>
+      </c>
+      <c r="J17" s="3" t="n">
         <v>128222</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="K17" s="3" t="n">
         <v>2559</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
-        <v>pyridoxal_5_phosphate_plp</v>
-      </c>
-      <c r="B18" s="2" t="n">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>pyridoxal_5_phosphate_plp</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="4" t="n">
         <v>0.66</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="2" t="n">
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="3" t="n">
         <v>910</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="K18" s="3" t="n">
         <v>455</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
-        <v>folic_acid</v>
-      </c>
-      <c r="B19" s="2" t="n">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>folic_acid</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="4" t="n">
         <v>0.763684907213091</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="4" t="n">
         <v>0.4977287644658298</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="4" t="n">
         <v>1.171634754891342</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>0.1760383687429629</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>3.312997283885483</v>
-      </c>
-      <c r="H19" s="4" t="n">
+      <c r="F19" s="4" t="n">
+        <v>0.1760383687429625</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>3.312997283885492</v>
+      </c>
+      <c r="H19" s="5" t="n">
         <v>82.8</v>
       </c>
-      <c r="I19" s="5" t="n">
-        <v>0.5029725560828019</v>
-      </c>
-      <c r="J19" s="2" t="n">
+      <c r="I19" s="6" t="n">
+        <v>0.5029725560828014</v>
+      </c>
+      <c r="J19" s="3" t="n">
         <v>84212</v>
       </c>
-      <c r="K19" s="2" t="n">
+      <c r="K19" s="3" t="n">
         <v>3088</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
-        <v>lutein</v>
-      </c>
-      <c r="B20" s="2" t="n">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>lutein</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="4" t="n">
         <v>0.7710515858035663</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="4" t="n">
         <v>0.6804506362045877</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="4" t="n">
         <v>0.8737159116880344</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>0.6293674105587818</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>0.9446319240495011</v>
-      </c>
-      <c r="H20" s="4" t="n">
+      <c r="F20" s="4" t="n">
+        <v>0.6293674105587594</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0.9446319240495346</v>
+      </c>
+      <c r="H20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="5" t="n">
-        <v>0.5547361243986885</v>
-      </c>
-      <c r="J20" s="2" t="n">
+      <c r="I20" s="6" t="n">
+        <v>0.5547361243986886</v>
+      </c>
+      <c r="J20" s="3" t="n">
         <v>881922</v>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="K20" s="3" t="n">
         <v>4765</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
-        <v>betaine</v>
-      </c>
-      <c r="B21" s="2" t="n">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>betaine</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="4" t="n">
         <v>0.49</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="4" t="n">
         <v>1.24</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="2" t="n">
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="3" t="n">
         <v>77208</v>
       </c>
-      <c r="K21" s="2" t="n">
+      <c r="K21" s="3" t="n">
         <v>225</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str">
-        <v>choline</v>
-      </c>
-      <c r="B22" s="2" t="n">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>choline</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="C22" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="4" t="n">
         <v>0.48</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="2" t="n">
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="6" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
         <v>77208</v>
       </c>
-      <c r="K22" s="2" t="n">
+      <c r="K22" s="3" t="n">
         <v>225</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
-        <v>zeaxanthin</v>
-      </c>
-      <c r="B23" s="2" t="n">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>zeaxanthin</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C23" s="4" t="n">
         <v>0.7904917964964951</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="4" t="n">
         <v>0.6716620276620098</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="4" t="n">
         <v>0.9303448082414207</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="4" t="n">
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="5"/>
-      <c r="J23" s="2" t="n">
+      <c r="I23" s="6" t="inlineStr"/>
+      <c r="J23" s="3" t="n">
         <v>781129</v>
       </c>
-      <c r="K23" s="2" t="n">
+      <c r="K23" s="3" t="n">
         <v>2616</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
-        <v>vitamin_b3</v>
-      </c>
-      <c r="B24" s="2" t="n">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>vitamin_b3</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="C24" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="4" t="n">
         <v>1.07</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="2" t="n">
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="6" t="inlineStr"/>
+      <c r="J24" s="3" t="n">
         <v>2301</v>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="K24" s="3" t="n">
         <v>767</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
-        <v>vitamin_d</v>
-      </c>
-      <c r="B25" s="2" t="n">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>vitamin_d</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C25" s="4" t="n">
         <v>0.8195498933329256</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="4" t="n">
         <v>0.669984969788664</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="4" t="n">
         <v>1.002503127605795</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>0.4597556361221974</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>1.460910916344895</v>
-      </c>
-      <c r="H25" s="4" t="n">
+      <c r="F25" s="4" t="n">
+        <v>0.4597556361221973</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>1.460910916344896</v>
+      </c>
+      <c r="H25" s="5" t="n">
         <v>61.07</v>
       </c>
-      <c r="I25" s="5" t="n">
-        <v>0.8617561858267218</v>
-      </c>
-      <c r="J25" s="2" t="n">
+      <c r="I25" s="6" t="n">
+        <v>0.8617561858267219</v>
+      </c>
+      <c r="J25" s="3" t="n">
         <v>153812</v>
       </c>
-      <c r="K25" s="2" t="n">
+      <c r="K25" s="3" t="n">
         <v>2840</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
-        <v>vitamin_b2</v>
-      </c>
-      <c r="B26" s="2" t="n">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>vitamin_b2</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="C26" s="4" t="n">
         <v>0.839624928963621</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="4" t="n">
         <v>0.6772600220311205</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="4" t="n">
         <v>1.04101895716483</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>0.2083219291362036</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>3.384041345336461</v>
-      </c>
-      <c r="H26" s="4" t="n">
+      <c r="F26" s="4" t="n">
+        <v>0.2083219291303213</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>3.384041345432015</v>
+      </c>
+      <c r="H26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="5" t="n">
-        <v>0.2763513833592364</v>
-      </c>
-      <c r="J26" s="2" t="n">
+      <c r="I26" s="6" t="n">
+        <v>0.2763513833592366</v>
+      </c>
+      <c r="J26" s="3" t="n">
         <v>3861</v>
       </c>
-      <c r="K26" s="2" t="n">
+      <c r="K26" s="3" t="n">
         <v>1547</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
-        <v>total_dietary_fiber_intake</v>
-      </c>
-      <c r="B27" s="2" t="n">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>total_dietary_fiber_intake</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="C27" s="4" t="n">
         <v>0.8469615338010708</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="4" t="n">
         <v>0.6424925870144645</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="4" t="n">
         <v>1.116389703847493</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="4" t="n">
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="5" t="n">
         <v>59.38</v>
       </c>
-      <c r="I27" s="5"/>
-      <c r="J27" s="2" t="n">
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="3" t="n">
         <v>4410</v>
       </c>
-      <c r="K27" s="2" t="n">
+      <c r="K27" s="3" t="n">
         <v>1621</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
-        <v>insoluble_dietary_fiber_intake</v>
-      </c>
-      <c r="B28" s="2" t="n">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>insoluble_dietary_fiber_intake</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="C28" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="2" t="n">
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="6" t="inlineStr"/>
+      <c r="J28" s="3" t="n">
         <v>2301</v>
       </c>
-      <c r="K28" s="2" t="n">
+      <c r="K28" s="3" t="n">
         <v>767</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str">
-        <v>polyunsaturated_fat_pufa</v>
-      </c>
-      <c r="B29" s="2" t="n">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>polyunsaturated_fat_pufa</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C29" s="4" t="n">
         <v>0.9436499474367985</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="4" t="n">
         <v>0.521419697551558</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="4" t="n">
         <v>1.707618995615963</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>0.0005402638396333133</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>1648.222882919305</v>
-      </c>
-      <c r="H29" s="4" t="n">
+      <c r="F29" s="4" t="n">
+        <v>0.0005402638395516072</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>1648.222883168572</v>
+      </c>
+      <c r="H29" s="5" t="n">
         <v>93.27</v>
       </c>
-      <c r="I29" s="5" t="n">
-        <v>0.9211585701279433</v>
-      </c>
-      <c r="J29" s="2" t="n">
+      <c r="I29" s="6" t="n">
+        <v>0.9211585701279434</v>
+      </c>
+      <c r="J29" s="3" t="n">
         <v>861316</v>
       </c>
-      <c r="K29" s="2" t="n">
+      <c r="K29" s="3" t="n">
         <v>2507</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str">
-        <v>beta_carotene</v>
-      </c>
-      <c r="B30" s="2" t="n">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>beta_carotene</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C30" s="4" t="n">
         <v>0.9776534669582103</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D30" s="4" t="n">
         <v>0.7008229441190426</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="4" t="n">
         <v>1.363697826425325</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>0.2848991490981571</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>3.354893492946523</v>
-      </c>
-      <c r="H30" s="4" t="n">
+      <c r="F30" s="4" t="n">
+        <v>0.2848991490980958</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>3.354893492947245</v>
+      </c>
+      <c r="H30" s="5" t="n">
         <v>87.95</v>
       </c>
-      <c r="I30" s="5" t="n">
-        <v>0.7478484537865681</v>
-      </c>
-      <c r="J30" s="2" t="n">
+      <c r="I30" s="6" t="n">
+        <v>0.7478484537865678</v>
+      </c>
+      <c r="J30" s="3" t="n">
         <v>881922</v>
       </c>
-      <c r="K30" s="2" t="n">
+      <c r="K30" s="3" t="n">
         <v>4765</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="str">
-        <v>sugar_sweetened_beverage_intake</v>
-      </c>
-      <c r="B31" s="2" t="n">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sugar_sweetened_beverage_intake</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="C31" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="D31" s="3" t="n">
-        <v>0.94</v>
-      </c>
-      <c r="E31" s="3" t="n">
+      <c r="D31" s="4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E31" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="2" t="n">
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="6" t="inlineStr"/>
+      <c r="J31" s="3" t="n">
         <v>389220</v>
       </c>
-      <c r="K31" s="2" t="n">
+      <c r="K31" s="3" t="n">
         <v>888</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str">
-        <v>lycopene</v>
-      </c>
-      <c r="B32" s="2" t="n">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>lycopene</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="C32" s="4" t="n">
         <v>1.017450511698055</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="4" t="n">
         <v>0.7301538599450065</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="4" t="n">
         <v>1.417790962349503</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>0.0222760771545342</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>46.47162678478706</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>74.26</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>0.5668230804465442</v>
-      </c>
-      <c r="J32" s="2" t="n">
+      <c r="F32" s="4" t="n">
+        <v>0.02227607715280967</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>46.47162678838473</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>74.26000000000001</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>0.5668230804465443</v>
+      </c>
+      <c r="J32" s="3" t="n">
         <v>873444</v>
       </c>
-      <c r="K32" s="2" t="n">
+      <c r="K32" s="3" t="n">
         <v>2860</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str">
-        <v>animal_protein_intake</v>
-      </c>
-      <c r="B33" s="2" t="n">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>animal_protein_intake</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="C33" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="2" t="n">
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="6" t="inlineStr"/>
+      <c r="J33" s="3" t="n">
         <v>774952</v>
       </c>
-      <c r="K33" s="2" t="n">
+      <c r="K33" s="3" t="n">
         <v>1019</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
-        <v>processed_meat_intake</v>
-      </c>
-      <c r="B34" s="2" t="n">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>processed_meat_intake</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="C34" s="4" t="n">
         <v>1.148894298164554</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="4" t="n">
         <v>0.9362244820588583</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="4" t="n">
         <v>1.410014516884722</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>0.6286522321999999</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>2.099663439889117</v>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>77.01</v>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>0.009615835655054882</v>
-      </c>
-      <c r="J34" s="2" t="n">
+      <c r="F34" s="4" t="n">
+        <v>0.6286522321999992</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>2.099663439889119</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>77.01000000000001</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>0.009615835655054888</v>
+      </c>
+      <c r="J34" s="3" t="n">
         <v>1766660</v>
       </c>
-      <c r="K34" s="2" t="n">
+      <c r="K34" s="3" t="n">
         <v>5212</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
-        <v>vitamin_a</v>
-      </c>
-      <c r="B35" s="2" t="n">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>vitamin_a</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="C35" s="4" t="n">
         <v>1.227525064963178</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="4" t="n">
         <v>0.5259232444453181</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="4" t="n">
         <v>2.865377201601115</v>
       </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="4" t="n">
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="5" t="n">
         <v>92.64</v>
       </c>
-      <c r="I35" s="5"/>
-      <c r="J35" s="2" t="n">
+      <c r="I35" s="6" t="inlineStr"/>
+      <c r="J35" s="3" t="n">
         <v>4597</v>
       </c>
-      <c r="K35" s="2" t="n">
+      <c r="K35" s="3" t="n">
         <v>1909</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
-        <v>potassium</v>
-      </c>
-      <c r="B36" s="2" t="n">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>potassium</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="C36" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="4" t="n">
         <v>1.9</v>
       </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="2" t="n">
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="6" t="inlineStr"/>
+      <c r="J36" s="3" t="n">
         <v>120852</v>
       </c>
-      <c r="K36" s="2" t="n">
+      <c r="K36" s="3" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
-        <v>dietary_protein_intake</v>
-      </c>
-      <c r="B37" s="2" t="n">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dietary_protein_intake</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="C37" s="4" t="n">
         <v>1.303822063731362</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="D37" s="4" t="n">
         <v>0.7543491156730364</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="4" t="n">
         <v>2.253760151959979</v>
       </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="4" t="n">
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="5" t="n">
         <v>66.34</v>
       </c>
-      <c r="I37" s="5"/>
-      <c r="J37" s="2" t="n">
+      <c r="I37" s="6" t="inlineStr"/>
+      <c r="J37" s="3" t="n">
         <v>776349</v>
       </c>
-      <c r="K37" s="2" t="n">
+      <c r="K37" s="3" t="n">
         <v>2168</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
-        <v>yogurt</v>
-      </c>
-      <c r="B38" s="2" t="n">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>yogurt</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="C38" s="4" t="n">
         <v>1.31</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D38" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="4" t="n">
         <v>1.67</v>
       </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="2" t="n">
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="5" t="inlineStr"/>
+      <c r="I38" s="6" t="inlineStr"/>
+      <c r="J38" s="3" t="n">
         <v>1812</v>
       </c>
-      <c r="K38" s="2" t="n">
+      <c r="K38" s="3" t="n">
         <v>777</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
-        <v>ultra_processed_food_intake</v>
-      </c>
-      <c r="B39" s="2" t="n">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ultra_processed_food_intake</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="C39" s="4" t="n">
         <v>1.37520113442151</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="4" t="n">
         <v>1.02009932499359</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="4" t="n">
         <v>1.854101106672441</v>
       </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="4" t="n">
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="5"/>
-      <c r="J39" s="2" t="n">
+      <c r="I39" s="6" t="inlineStr"/>
+      <c r="J39" s="3" t="n">
         <v>647537</v>
       </c>
-      <c r="K39" s="2" t="n">
+      <c r="K39" s="3" t="n">
         <v>594</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
-        <v>monounsaturated_fat_mufa</v>
-      </c>
-      <c r="B40" s="2" t="n">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>monounsaturated_fat_mufa</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="C40" s="4" t="n">
         <v>1.39096812846378</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="D40" s="4" t="n">
         <v>0.8185670233008897</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="4" t="n">
         <v>2.363633373110901</v>
       </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="4" t="n">
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="5" t="n">
         <v>80.2</v>
       </c>
-      <c r="I40" s="5"/>
-      <c r="J40" s="2" t="n">
+      <c r="I40" s="6" t="inlineStr"/>
+      <c r="J40" s="3" t="n">
         <v>777095</v>
       </c>
-      <c r="K40" s="2" t="n">
+      <c r="K40" s="3" t="n">
         <v>1801</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str">
-        <v>red_meat</v>
-      </c>
-      <c r="B41" s="2" t="n">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>red_meat</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="C41" s="4" t="n">
         <v>1.428035894777088</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="4" t="n">
         <v>1.125806874101985</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="4" t="n">
         <v>1.811399951166991</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>0.6711000405372343</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>3.03872208849711</v>
-      </c>
-      <c r="H41" s="4" t="n">
+      <c r="F41" s="4" t="n">
+        <v>0.6711000405372333</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>3.038722088497114</v>
+      </c>
+      <c r="H41" s="5" t="n">
         <v>81.58</v>
       </c>
-      <c r="I41" s="5" t="n">
-        <v>0.01776300266501832</v>
-      </c>
-      <c r="J41" s="2" t="n">
+      <c r="I41" s="6" t="n">
+        <v>0.01776300266501834</v>
+      </c>
+      <c r="J41" s="3" t="n">
         <v>1768446</v>
       </c>
-      <c r="K41" s="2" t="n">
+      <c r="K41" s="3" t="n">
         <v>5800</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="str">
-        <v>docosahexaenoic_acid</v>
-      </c>
-      <c r="B42" s="2" t="n">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>docosahexaenoic_acid</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="C42" s="4" t="n">
         <v>1.56</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="4" t="n">
         <v>1.07</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="4" t="n">
         <v>2.27</v>
       </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="2" t="n">
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="5" t="inlineStr"/>
+      <c r="I42" s="6" t="inlineStr"/>
+      <c r="J42" s="3" t="n">
         <v>84063</v>
       </c>
-      <c r="K42" s="2" t="n">
+      <c r="K42" s="3" t="n">
         <v>262</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="str">
-        <v>omega_3_fatty_acids</v>
-      </c>
-      <c r="B43" s="2" t="n">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>omega_3_fatty_acids</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="C43" s="4" t="n">
         <v>1.56</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="D43" s="4" t="n">
         <v>1.07</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="4" t="n">
         <v>2.28</v>
       </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="2" t="n">
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr"/>
+      <c r="H43" s="5" t="inlineStr"/>
+      <c r="I43" s="6" t="inlineStr"/>
+      <c r="J43" s="3" t="n">
         <v>84063</v>
       </c>
-      <c r="K43" s="2" t="n">
+      <c r="K43" s="3" t="n">
         <v>262</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="str">
-        <v>oleic_acid</v>
-      </c>
-      <c r="B44" s="2" t="n">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>oleic_acid</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="C44" s="4" t="n">
         <v>1.9</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="D44" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="4" t="n">
         <v>2.9</v>
       </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="2" t="n">
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr"/>
+      <c r="H44" s="5" t="inlineStr"/>
+      <c r="I44" s="6" t="inlineStr"/>
+      <c r="J44" s="3" t="n">
         <v>2143</v>
       </c>
-      <c r="K44" s="2" t="n">
+      <c r="K44" s="3" t="n">
         <v>323</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="str">
-        <v>omega_9_fatty_acids</v>
-      </c>
-      <c r="B45" s="2" t="n">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>omega_9_fatty_acids</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="C45" s="4" t="n">
         <v>1.9</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="D45" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E45" s="4" t="n">
         <v>2.9</v>
       </c>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="2" t="n">
+      <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="5" t="inlineStr"/>
+      <c r="I45" s="6" t="inlineStr"/>
+      <c r="J45" s="3" t="n">
         <v>2143</v>
       </c>
-      <c r="K45" s="2" t="n">
+      <c r="K45" s="3" t="n">
         <v>323</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="str">
-        <v>carnitine</v>
-      </c>
-      <c r="B46" s="2" t="n">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>carnitine</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="C46" s="4" t="n">
         <v>2.39</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="D46" s="4" t="n">
         <v>1.39</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="4" t="n">
         <v>4.13</v>
       </c>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="2" t="n">
+      <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr"/>
+      <c r="I46" s="6" t="inlineStr"/>
+      <c r="J46" s="3" t="n">
         <v>534</v>
       </c>
-      <c r="K46" s="2" t="n">
+      <c r="K46" s="3" t="n">
         <v>267</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="str">
-        <v>dairy</v>
-      </c>
-      <c r="B47" s="2" t="n">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="C47" s="4" t="n">
         <v>2.715293362405407</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="D47" s="4" t="n">
         <v>1.217987613870554</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="E47" s="4" t="n">
         <v>6.052673044477135</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>0.0003047814843853535</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>24190.50507215516</v>
-      </c>
-      <c r="H47" s="4" t="n">
+      <c r="F47" s="4" t="n">
+        <v>0.0003047814843291999</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>24190.50507661207</v>
+      </c>
+      <c r="H47" s="5" t="n">
         <v>73.78</v>
       </c>
-      <c r="I47" s="5" t="n">
+      <c r="I47" s="6" t="n">
         <v>0.1029158875214485</v>
       </c>
-      <c r="J47" s="2" t="n">
+      <c r="J47" s="3" t="n">
         <v>3506</v>
       </c>
-      <c r="K47" s="2" t="n">
+      <c r="K47" s="3" t="n">
         <v>1009</v>
       </c>
     </row>

--- a/summary/yes/exposures_meta_analysis_renal_cell_carcinoma_combined.xlsx
+++ b/summary/yes/exposures_meta_analysis_renal_cell_carcinoma_combined.xlsx
@@ -23,16 +23,13 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -52,7 +49,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -60,22 +57,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -464,57 +452,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>number estimates</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -526,26 +514,26 @@
           <t>green_tea</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="3" t="n">
         <v>0.34</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="6" t="inlineStr"/>
-      <c r="J2" s="3" t="n">
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
         <v>549</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="2" t="n">
         <v>250</v>
       </c>
     </row>
@@ -555,26 +543,26 @@
           <t>linoleic_acid</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr"/>
-      <c r="J3" s="3" t="n">
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
         <v>2301</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="2" t="n">
         <v>767</v>
       </c>
     </row>
@@ -584,26 +572,26 @@
           <t>omega_6_fatty_acids</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="3" t="n">
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
         <v>2301</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="2" t="n">
         <v>767</v>
       </c>
     </row>
@@ -613,26 +601,26 @@
           <t>tomato</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="3" t="n">
         <v>0.31</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="3" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="6" t="inlineStr"/>
-      <c r="J5" s="3" t="n">
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="2" t="n">
         <v>672</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="2" t="n">
         <v>335</v>
       </c>
     </row>
@@ -642,28 +630,28 @@
           <t>selenium</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="3" t="n">
         <v>0.5277144267608633</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="3" t="n">
         <v>0.03896077142373314</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="3" t="n">
         <v>7.148481810757238</v>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="5" t="n">
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="n">
         <v>98.91</v>
       </c>
-      <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="3" t="n">
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="2" t="n">
         <v>3471</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="2" t="n">
         <v>1543</v>
       </c>
     </row>
@@ -673,26 +661,26 @@
           <t>quercetin</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="3" t="n">
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="2" t="n">
         <v>27111</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="2" t="n">
         <v>228</v>
       </c>
     </row>
@@ -702,28 +690,28 @@
           <t>calcium</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="3" t="n">
         <v>0.6182267372856237</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="3" t="n">
         <v>0.159119466063619</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="3" t="n">
         <v>2.40223607137391</v>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="5" t="n">
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="n">
         <v>93.7</v>
       </c>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="3" t="n">
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="2" t="n">
         <v>2273</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="2" t="n">
         <v>154</v>
       </c>
     </row>
@@ -733,28 +721,28 @@
           <t>vitamin_b12</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="3" t="n">
         <v>0.6305265594747873</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="3" t="n">
         <v>0.4657994976498283</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="3" t="n">
         <v>0.8535083103545701</v>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="5" t="n">
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="3" t="n">
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="2" t="n">
         <v>1959</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="2" t="n">
         <v>730</v>
       </c>
     </row>
@@ -764,26 +752,26 @@
           <t>eggs</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="3" t="n">
         <v>0.64</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="3" t="n">
         <v>0.48</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="6" t="inlineStr"/>
-      <c r="J10" s="3" t="n">
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="2" t="n">
         <v>1812</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" s="2" t="n">
         <v>777</v>
       </c>
     </row>
@@ -793,34 +781,34 @@
           <t>vitamin_e</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="3" t="n">
         <v>0.6704541234521412</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="3" t="n">
         <v>0.4526663314814308</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="3" t="n">
         <v>0.9929251454538985</v>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>0.1198875658484078</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>3.749419120097587</v>
-      </c>
-      <c r="H11" s="5" t="n">
+      <c r="F11" s="3" t="n">
+        <v>0.1198875658458503</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>3.749419120177575</v>
+      </c>
+      <c r="H11" s="4" t="n">
         <v>75.61</v>
       </c>
-      <c r="I11" s="6" t="n">
-        <v>0.5015932102841116</v>
-      </c>
-      <c r="J11" s="3" t="n">
+      <c r="I11" s="5" t="n">
+        <v>0.5015932102841113</v>
+      </c>
+      <c r="J11" s="2" t="n">
         <v>127855</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="2" t="n">
         <v>2404</v>
       </c>
     </row>
@@ -830,26 +818,26 @@
           <t>anti_inflammatory_diet</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="3" t="n">
         <v>0.68</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="3" t="n">
         <v>0.52</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="6" t="inlineStr"/>
-      <c r="J12" s="3" t="n">
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="2" t="n">
         <v>71421</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="2" t="n">
         <v>431</v>
       </c>
     </row>
@@ -859,28 +847,28 @@
           <t>vitamin_b1</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="3" t="n">
         <v>0.7116279829325146</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="3" t="n">
         <v>0.5506807713861427</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="3" t="n">
         <v>0.9196151607361948</v>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="5" t="n">
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="3" t="n">
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="2" t="n">
         <v>4597</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="2" t="n">
         <v>1909</v>
       </c>
     </row>
@@ -890,34 +878,34 @@
           <t>tea</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="3" t="n">
         <v>0.7142658835761514</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="3" t="n">
         <v>0.5123229966574786</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="3" t="n">
         <v>0.9958088076649545</v>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>0.1670242223327739</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>3.054501588544217</v>
-      </c>
-      <c r="H14" s="5" t="n">
+      <c r="F14" s="3" t="n">
+        <v>0.1670242223297662</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>3.054501588599221</v>
+      </c>
+      <c r="H14" s="4" t="n">
         <v>77.67</v>
       </c>
-      <c r="I14" s="6" t="n">
-        <v>0.4060945257413281</v>
-      </c>
-      <c r="J14" s="3" t="n">
+      <c r="I14" s="5" t="n">
+        <v>0.4060945257413278</v>
+      </c>
+      <c r="J14" s="2" t="n">
         <v>804643</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="2" t="n">
         <v>2861</v>
       </c>
     </row>
@@ -927,34 +915,34 @@
           <t>alcohol</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="3" t="n">
         <v>0.7166985207200148</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="3" t="n">
         <v>0.6540967517572572</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="3" t="n">
         <v>0.785291729736156</v>
       </c>
-      <c r="F15" s="4" t="n">
-        <v>0.5315702982473401</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>0.9663007344388015</v>
-      </c>
-      <c r="H15" s="5" t="n">
+      <c r="F15" s="3" t="n">
+        <v>0.5315702982473368</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0.9663007344388077</v>
+      </c>
+      <c r="H15" s="4" t="n">
         <v>52.61</v>
       </c>
-      <c r="I15" s="6" t="n">
-        <v>0.00190499440164191</v>
-      </c>
-      <c r="J15" s="3" t="n">
+      <c r="I15" s="5" t="n">
+        <v>0.001904994401641916</v>
+      </c>
+      <c r="J15" s="2" t="n">
         <v>3860985</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="2" t="n">
         <v>11926</v>
       </c>
     </row>
@@ -964,34 +952,34 @@
           <t>vitamin_b6</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="3" t="n">
         <v>0.7345479521991701</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="3" t="n">
         <v>0.5184042166537559</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="3" t="n">
         <v>1.040706698318849</v>
       </c>
-      <c r="F16" s="4" t="n">
-        <v>0.1585301081313205</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>3.403521895241767</v>
-      </c>
-      <c r="H16" s="5" t="n">
+      <c r="F16" s="3" t="n">
+        <v>0.1585301081283082</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>3.403521895306439</v>
+      </c>
+      <c r="H16" s="4" t="n">
         <v>81.53</v>
       </c>
-      <c r="I16" s="6" t="n">
-        <v>0.9763185191218325</v>
-      </c>
-      <c r="J16" s="3" t="n">
+      <c r="I16" s="5" t="n">
+        <v>0.9763185191218329</v>
+      </c>
+      <c r="J16" s="2" t="n">
         <v>4771</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="2" t="n">
         <v>2002</v>
       </c>
     </row>
@@ -1001,34 +989,34 @@
           <t>vitamin_c</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="3" t="n">
         <v>0.7585094662858782</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="3" t="n">
         <v>0.6137301147444475</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="3" t="n">
         <v>0.9374423653381478</v>
       </c>
-      <c r="F17" s="4" t="n">
-        <v>0.4223806276718763</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>1.36212830975817</v>
-      </c>
-      <c r="H17" s="5" t="n">
+      <c r="F17" s="3" t="n">
+        <v>0.4223806276719194</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>1.362128309758031</v>
+      </c>
+      <c r="H17" s="4" t="n">
         <v>39.11</v>
       </c>
-      <c r="I17" s="6" t="n">
-        <v>0.2965256086013331</v>
-      </c>
-      <c r="J17" s="3" t="n">
+      <c r="I17" s="5" t="n">
+        <v>0.2965256086013334</v>
+      </c>
+      <c r="J17" s="2" t="n">
         <v>128222</v>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" s="2" t="n">
         <v>2559</v>
       </c>
     </row>
@@ -1038,26 +1026,26 @@
           <t>pyridoxal_5_phosphate_plp</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="3" t="n">
         <v>0.66</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="3" t="n">
         <v>0.87</v>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="6" t="inlineStr"/>
-      <c r="J18" s="3" t="n">
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="2" t="n">
         <v>910</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="2" t="n">
         <v>455</v>
       </c>
     </row>
@@ -1067,34 +1055,34 @@
           <t>folic_acid</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="3" t="n">
         <v>0.763684907213091</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="3" t="n">
         <v>0.4977287644658298</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="3" t="n">
         <v>1.171634754891342</v>
       </c>
-      <c r="F19" s="4" t="n">
-        <v>0.1760383687429625</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>3.312997283885492</v>
-      </c>
-      <c r="H19" s="5" t="n">
+      <c r="F19" s="3" t="n">
+        <v>0.1760383687429629</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>3.312997283885483</v>
+      </c>
+      <c r="H19" s="4" t="n">
         <v>82.8</v>
       </c>
-      <c r="I19" s="6" t="n">
-        <v>0.5029725560828014</v>
-      </c>
-      <c r="J19" s="3" t="n">
+      <c r="I19" s="5" t="n">
+        <v>0.5029725560828019</v>
+      </c>
+      <c r="J19" s="2" t="n">
         <v>84212</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="2" t="n">
         <v>3088</v>
       </c>
     </row>
@@ -1104,34 +1092,34 @@
           <t>lutein</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="3" t="n">
         <v>0.7710515858035663</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="3" t="n">
         <v>0.6804506362045877</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="3" t="n">
         <v>0.8737159116880344</v>
       </c>
-      <c r="F20" s="4" t="n">
-        <v>0.6293674105587594</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>0.9446319240495346</v>
-      </c>
-      <c r="H20" s="5" t="n">
+      <c r="F20" s="3" t="n">
+        <v>0.6293674105587818</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0.9446319240495011</v>
+      </c>
+      <c r="H20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="6" t="n">
-        <v>0.5547361243986886</v>
-      </c>
-      <c r="J20" s="3" t="n">
+      <c r="I20" s="5" t="n">
+        <v>0.5547361243986885</v>
+      </c>
+      <c r="J20" s="2" t="n">
         <v>881922</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="2" t="n">
         <v>4765</v>
       </c>
     </row>
@@ -1141,26 +1129,26 @@
           <t>betaine</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="3" t="n">
         <v>0.49</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="3" t="n">
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
         <v>77208</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="2" t="n">
         <v>225</v>
       </c>
     </row>
@@ -1170,26 +1158,26 @@
           <t>choline</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="3" t="n">
         <v>0.48</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="6" t="inlineStr"/>
-      <c r="J22" s="3" t="n">
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
         <v>77208</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="2" t="n">
         <v>225</v>
       </c>
     </row>
@@ -1199,28 +1187,28 @@
           <t>zeaxanthin</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="3" t="n">
         <v>0.7904917964964951</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="3" t="n">
         <v>0.6716620276620098</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="3" t="n">
         <v>0.9303448082414207</v>
       </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="5" t="n">
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="6" t="inlineStr"/>
-      <c r="J23" s="3" t="n">
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="2" t="n">
         <v>781129</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="2" t="n">
         <v>2616</v>
       </c>
     </row>
@@ -1230,26 +1218,26 @@
           <t>vitamin_b3</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="3" t="n">
         <v>1.07</v>
       </c>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="6" t="inlineStr"/>
-      <c r="J24" s="3" t="n">
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="2" t="n">
         <v>2301</v>
       </c>
-      <c r="K24" s="3" t="n">
+      <c r="K24" s="2" t="n">
         <v>767</v>
       </c>
     </row>
@@ -1259,34 +1247,34 @@
           <t>vitamin_d</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="C25" s="3" t="n">
         <v>0.8195498933329256</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="3" t="n">
         <v>0.669984969788664</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="3" t="n">
         <v>1.002503127605795</v>
       </c>
-      <c r="F25" s="4" t="n">
-        <v>0.4597556361221973</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>1.460910916344896</v>
-      </c>
-      <c r="H25" s="5" t="n">
+      <c r="F25" s="3" t="n">
+        <v>0.4597556361221974</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>1.460910916344895</v>
+      </c>
+      <c r="H25" s="4" t="n">
         <v>61.07</v>
       </c>
-      <c r="I25" s="6" t="n">
-        <v>0.8617561858267219</v>
-      </c>
-      <c r="J25" s="3" t="n">
+      <c r="I25" s="5" t="n">
+        <v>0.8617561858267218</v>
+      </c>
+      <c r="J25" s="2" t="n">
         <v>153812</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="2" t="n">
         <v>2840</v>
       </c>
     </row>
@@ -1296,34 +1284,34 @@
           <t>vitamin_b2</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B26" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" s="3" t="n">
         <v>0.839624928963621</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="3" t="n">
         <v>0.6772600220311205</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="3" t="n">
         <v>1.04101895716483</v>
       </c>
-      <c r="F26" s="4" t="n">
-        <v>0.2083219291303213</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>3.384041345432015</v>
-      </c>
-      <c r="H26" s="5" t="n">
+      <c r="F26" s="3" t="n">
+        <v>0.2083219291362036</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>3.384041345336461</v>
+      </c>
+      <c r="H26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="6" t="n">
-        <v>0.2763513833592366</v>
-      </c>
-      <c r="J26" s="3" t="n">
+      <c r="I26" s="5" t="n">
+        <v>0.2763513833592364</v>
+      </c>
+      <c r="J26" s="2" t="n">
         <v>3861</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="2" t="n">
         <v>1547</v>
       </c>
     </row>
@@ -1333,28 +1321,28 @@
           <t>total_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C27" s="4" t="n">
+      <c r="C27" s="3" t="n">
         <v>0.8469615338010708</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="3" t="n">
         <v>0.6424925870144645</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="3" t="n">
         <v>1.116389703847493</v>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="5" t="n">
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="4" t="n">
         <v>59.38</v>
       </c>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="3" t="n">
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="2" t="n">
         <v>4410</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="2" t="n">
         <v>1621</v>
       </c>
     </row>
@@ -1364,26 +1352,26 @@
           <t>insoluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="C28" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="6" t="inlineStr"/>
-      <c r="J28" s="3" t="n">
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="2" t="n">
         <v>2301</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="2" t="n">
         <v>767</v>
       </c>
     </row>
@@ -1393,34 +1381,34 @@
           <t>polyunsaturated_fat_pufa</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n">
+      <c r="B29" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="4" t="n">
+      <c r="C29" s="3" t="n">
         <v>0.9436499474367985</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="3" t="n">
         <v>0.521419697551558</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="3" t="n">
         <v>1.707618995615963</v>
       </c>
-      <c r="F29" s="4" t="n">
-        <v>0.0005402638395516072</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>1648.222883168572</v>
-      </c>
-      <c r="H29" s="5" t="n">
+      <c r="F29" s="3" t="n">
+        <v>0.0005402638396333133</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>1648.222882919305</v>
+      </c>
+      <c r="H29" s="4" t="n">
         <v>93.27</v>
       </c>
-      <c r="I29" s="6" t="n">
-        <v>0.9211585701279434</v>
-      </c>
-      <c r="J29" s="3" t="n">
+      <c r="I29" s="5" t="n">
+        <v>0.9211585701279433</v>
+      </c>
+      <c r="J29" s="2" t="n">
         <v>861316</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="2" t="n">
         <v>2507</v>
       </c>
     </row>
@@ -1430,34 +1418,34 @@
           <t>beta_carotene</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
+      <c r="B30" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C30" s="4" t="n">
+      <c r="C30" s="3" t="n">
         <v>0.9776534669582103</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="3" t="n">
         <v>0.7008229441190426</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="3" t="n">
         <v>1.363697826425325</v>
       </c>
-      <c r="F30" s="4" t="n">
-        <v>0.2848991490980958</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>3.354893492947245</v>
-      </c>
-      <c r="H30" s="5" t="n">
+      <c r="F30" s="3" t="n">
+        <v>0.2848991490981571</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>3.354893492946523</v>
+      </c>
+      <c r="H30" s="4" t="n">
         <v>87.95</v>
       </c>
-      <c r="I30" s="6" t="n">
-        <v>0.7478484537865678</v>
-      </c>
-      <c r="J30" s="3" t="n">
+      <c r="I30" s="5" t="n">
+        <v>0.7478484537865681</v>
+      </c>
+      <c r="J30" s="2" t="n">
         <v>881922</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="2" t="n">
         <v>4765</v>
       </c>
     </row>
@@ -1467,26 +1455,26 @@
           <t>sugar_sweetened_beverage_intake</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="C31" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="3" t="n">
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="2" t="n">
         <v>389220</v>
       </c>
-      <c r="K31" s="3" t="n">
+      <c r="K31" s="2" t="n">
         <v>888</v>
       </c>
     </row>
@@ -1496,34 +1484,34 @@
           <t>lycopene</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" s="3" t="n">
         <v>1.017450511698055</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="3" t="n">
         <v>0.7301538599450065</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="3" t="n">
         <v>1.417790962349503</v>
       </c>
-      <c r="F32" s="4" t="n">
-        <v>0.02227607715280967</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>46.47162678838473</v>
-      </c>
-      <c r="H32" s="5" t="n">
+      <c r="F32" s="3" t="n">
+        <v>0.0222760771545342</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>46.47162678478706</v>
+      </c>
+      <c r="H32" s="4" t="n">
         <v>74.26000000000001</v>
       </c>
-      <c r="I32" s="6" t="n">
-        <v>0.5668230804465443</v>
-      </c>
-      <c r="J32" s="3" t="n">
+      <c r="I32" s="5" t="n">
+        <v>0.5668230804465442</v>
+      </c>
+      <c r="J32" s="2" t="n">
         <v>873444</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="2" t="n">
         <v>2860</v>
       </c>
     </row>
@@ -1533,26 +1521,26 @@
           <t>animal_protein_intake</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n">
+      <c r="B33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="3" t="n">
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="2" t="n">
         <v>774952</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="2" t="n">
         <v>1019</v>
       </c>
     </row>
@@ -1562,34 +1550,34 @@
           <t>processed_meat_intake</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
+      <c r="B34" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="C34" s="3" t="n">
         <v>1.148894298164554</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="3" t="n">
         <v>0.9362244820588583</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="3" t="n">
         <v>1.410014516884722</v>
       </c>
-      <c r="F34" s="4" t="n">
-        <v>0.6286522321999992</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>2.099663439889119</v>
-      </c>
-      <c r="H34" s="5" t="n">
+      <c r="F34" s="3" t="n">
+        <v>0.6286522321999999</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>2.099663439889117</v>
+      </c>
+      <c r="H34" s="4" t="n">
         <v>77.01000000000001</v>
       </c>
-      <c r="I34" s="6" t="n">
-        <v>0.009615835655054888</v>
-      </c>
-      <c r="J34" s="3" t="n">
+      <c r="I34" s="5" t="n">
+        <v>0.009615835655054882</v>
+      </c>
+      <c r="J34" s="2" t="n">
         <v>1766660</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="2" t="n">
         <v>5212</v>
       </c>
     </row>
@@ -1599,28 +1587,28 @@
           <t>vitamin_a</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
+      <c r="B35" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C35" s="4" t="n">
+      <c r="C35" s="3" t="n">
         <v>1.227525064963178</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="3" t="n">
         <v>0.5259232444453181</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="3" t="n">
         <v>2.865377201601115</v>
       </c>
-      <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="4" t="inlineStr"/>
-      <c r="H35" s="5" t="n">
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="4" t="n">
         <v>92.64</v>
       </c>
-      <c r="I35" s="6" t="inlineStr"/>
-      <c r="J35" s="3" t="n">
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="2" t="n">
         <v>4597</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="2" t="n">
         <v>1909</v>
       </c>
     </row>
@@ -1630,26 +1618,26 @@
           <t>potassium</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n">
+      <c r="B36" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="4" t="n">
+      <c r="C36" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="3" t="n">
         <v>0.87</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="4" t="inlineStr"/>
-      <c r="H36" s="5" t="inlineStr"/>
-      <c r="I36" s="6" t="inlineStr"/>
-      <c r="J36" s="3" t="n">
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="2" t="n">
         <v>120852</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="2" t="n">
         <v>485</v>
       </c>
     </row>
@@ -1659,28 +1647,28 @@
           <t>dietary_protein_intake</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n">
+      <c r="B37" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="4" t="n">
+      <c r="C37" s="3" t="n">
         <v>1.303822063731362</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="3" t="n">
         <v>0.7543491156730364</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E37" s="3" t="n">
         <v>2.253760151959979</v>
       </c>
-      <c r="F37" s="4" t="inlineStr"/>
-      <c r="G37" s="4" t="inlineStr"/>
-      <c r="H37" s="5" t="n">
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="4" t="n">
         <v>66.34</v>
       </c>
-      <c r="I37" s="6" t="inlineStr"/>
-      <c r="J37" s="3" t="n">
+      <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="2" t="n">
         <v>776349</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="2" t="n">
         <v>2168</v>
       </c>
     </row>
@@ -1690,26 +1678,26 @@
           <t>yogurt</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n">
+      <c r="B38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="4" t="n">
+      <c r="C38" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="E38" s="4" t="n">
+      <c r="E38" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="6" t="inlineStr"/>
-      <c r="J38" s="3" t="n">
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="2" t="n">
         <v>1812</v>
       </c>
-      <c r="K38" s="3" t="n">
+      <c r="K38" s="2" t="n">
         <v>777</v>
       </c>
     </row>
@@ -1719,28 +1707,28 @@
           <t>ultra_processed_food_intake</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n">
+      <c r="B39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C39" s="4" t="n">
+      <c r="C39" s="3" t="n">
         <v>1.37520113442151</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="3" t="n">
         <v>1.02009932499359</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="3" t="n">
         <v>1.854101106672441</v>
       </c>
-      <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr"/>
-      <c r="H39" s="5" t="n">
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="6" t="inlineStr"/>
-      <c r="J39" s="3" t="n">
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="2" t="n">
         <v>647537</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="2" t="n">
         <v>594</v>
       </c>
     </row>
@@ -1750,28 +1738,28 @@
           <t>monounsaturated_fat_mufa</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n">
+      <c r="B40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C40" s="4" t="n">
+      <c r="C40" s="3" t="n">
         <v>1.39096812846378</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="3" t="n">
         <v>0.8185670233008897</v>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="E40" s="3" t="n">
         <v>2.363633373110901</v>
       </c>
-      <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="4" t="inlineStr"/>
-      <c r="H40" s="5" t="n">
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="4" t="n">
         <v>80.2</v>
       </c>
-      <c r="I40" s="6" t="inlineStr"/>
-      <c r="J40" s="3" t="n">
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="2" t="n">
         <v>777095</v>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="2" t="n">
         <v>1801</v>
       </c>
     </row>
@@ -1781,34 +1769,34 @@
           <t>red_meat</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n">
+      <c r="B41" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C41" s="4" t="n">
+      <c r="C41" s="3" t="n">
         <v>1.428035894777088</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="3" t="n">
         <v>1.125806874101985</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="3" t="n">
         <v>1.811399951166991</v>
       </c>
-      <c r="F41" s="4" t="n">
-        <v>0.6711000405372333</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>3.038722088497114</v>
-      </c>
-      <c r="H41" s="5" t="n">
+      <c r="F41" s="3" t="n">
+        <v>0.6711000405372343</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>3.03872208849711</v>
+      </c>
+      <c r="H41" s="4" t="n">
         <v>81.58</v>
       </c>
-      <c r="I41" s="6" t="n">
-        <v>0.01776300266501834</v>
-      </c>
-      <c r="J41" s="3" t="n">
+      <c r="I41" s="5" t="n">
+        <v>0.01776300266501832</v>
+      </c>
+      <c r="J41" s="2" t="n">
         <v>1768446</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="2" t="n">
         <v>5800</v>
       </c>
     </row>
@@ -1818,26 +1806,26 @@
           <t>docosahexaenoic_acid</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n">
+      <c r="B42" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C42" s="4" t="n">
+      <c r="C42" s="3" t="n">
         <v>1.56</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="3" t="n">
         <v>1.07</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="3" t="n">
         <v>2.27</v>
       </c>
-      <c r="F42" s="4" t="inlineStr"/>
-      <c r="G42" s="4" t="inlineStr"/>
-      <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="6" t="inlineStr"/>
-      <c r="J42" s="3" t="n">
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="2" t="n">
         <v>84063</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="2" t="n">
         <v>262</v>
       </c>
     </row>
@@ -1847,26 +1835,26 @@
           <t>omega_3_fatty_acids</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n">
+      <c r="B43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="4" t="n">
+      <c r="C43" s="3" t="n">
         <v>1.56</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="3" t="n">
         <v>1.07</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" s="3" t="n">
         <v>2.28</v>
       </c>
-      <c r="F43" s="4" t="inlineStr"/>
-      <c r="G43" s="4" t="inlineStr"/>
-      <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="6" t="inlineStr"/>
-      <c r="J43" s="3" t="n">
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="2" t="n">
         <v>84063</v>
       </c>
-      <c r="K43" s="3" t="n">
+      <c r="K43" s="2" t="n">
         <v>262</v>
       </c>
     </row>
@@ -1876,26 +1864,26 @@
           <t>oleic_acid</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n">
+      <c r="B44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C44" s="4" t="n">
+      <c r="C44" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="E44" s="4" t="n">
+      <c r="E44" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="F44" s="4" t="inlineStr"/>
-      <c r="G44" s="4" t="inlineStr"/>
-      <c r="H44" s="5" t="inlineStr"/>
-      <c r="I44" s="6" t="inlineStr"/>
-      <c r="J44" s="3" t="n">
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="2" t="n">
         <v>2143</v>
       </c>
-      <c r="K44" s="3" t="n">
+      <c r="K44" s="2" t="n">
         <v>323</v>
       </c>
     </row>
@@ -1905,26 +1893,26 @@
           <t>omega_9_fatty_acids</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n">
+      <c r="B45" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C45" s="4" t="n">
+      <c r="C45" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="F45" s="4" t="inlineStr"/>
-      <c r="G45" s="4" t="inlineStr"/>
-      <c r="H45" s="5" t="inlineStr"/>
-      <c r="I45" s="6" t="inlineStr"/>
-      <c r="J45" s="3" t="n">
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="5" t="inlineStr"/>
+      <c r="J45" s="2" t="n">
         <v>2143</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="2" t="n">
         <v>323</v>
       </c>
     </row>
@@ -1934,26 +1922,26 @@
           <t>carnitine</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n">
+      <c r="B46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C46" s="4" t="n">
+      <c r="C46" s="3" t="n">
         <v>2.39</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="3" t="n">
         <v>1.39</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E46" s="3" t="n">
         <v>4.13</v>
       </c>
-      <c r="F46" s="4" t="inlineStr"/>
-      <c r="G46" s="4" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="6" t="inlineStr"/>
-      <c r="J46" s="3" t="n">
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="2" t="n">
         <v>534</v>
       </c>
-      <c r="K46" s="3" t="n">
+      <c r="K46" s="2" t="n">
         <v>267</v>
       </c>
     </row>
@@ -1963,34 +1951,34 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n">
+      <c r="B47" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C47" s="4" t="n">
+      <c r="C47" s="3" t="n">
         <v>2.715293362405407</v>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D47" s="3" t="n">
         <v>1.217987613870554</v>
       </c>
-      <c r="E47" s="4" t="n">
+      <c r="E47" s="3" t="n">
         <v>6.052673044477135</v>
       </c>
-      <c r="F47" s="4" t="n">
-        <v>0.0003047814843291999</v>
-      </c>
-      <c r="G47" s="4" t="n">
-        <v>24190.50507661207</v>
-      </c>
-      <c r="H47" s="5" t="n">
+      <c r="F47" s="3" t="n">
+        <v>0.0003047814843853535</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>24190.50507215516</v>
+      </c>
+      <c r="H47" s="4" t="n">
         <v>73.78</v>
       </c>
-      <c r="I47" s="6" t="n">
+      <c r="I47" s="5" t="n">
         <v>0.1029158875214485</v>
       </c>
-      <c r="J47" s="3" t="n">
+      <c r="J47" s="2" t="n">
         <v>3506</v>
       </c>
-      <c r="K47" s="3" t="n">
+      <c r="K47" s="2" t="n">
         <v>1009</v>
       </c>
     </row>
